--- a/07-Spare Parts Stock/spare-parts-stock-testcases.xlsx
+++ b/07-Spare Parts Stock/spare-parts-stock-testcases.xlsx
@@ -331,7 +331,7 @@
     <t>Store: Store1</t>
   </si>
   <si>
-    <t>Success toast "Spare parts serial updated successfully"; row SN0000019 updated to Store=Store1 in the list</t>
+    <t>Success toast "Spare Parts Stock updated successfully"; row SN0000019 updated to Store=Store1 in the list</t>
   </si>
   <si>
     <t>TS-04</t>
@@ -369,7 +369,7 @@
     <t>Click Delete and confirm in the confirm dialog</t>
   </si>
   <si>
-    <t>Confirm dialog appears; after confirm, toast "Spare parts serial deleted successfully"; row SN0000016 disappears; iPhone 17 Pro Screen stock count on Spare Parts master decreases by 1</t>
+    <t>Confirm dialog appears; after confirm, toast "Spare Parts Stock deleted successfully"; row SN0000016 disappears; iPhone 17 Pro Screen stock count on Spare Parts master decreases by 1</t>
   </si>
   <si>
     <t>TS-04_TC-03</t>
@@ -570,7 +570,7 @@
     <t>Serial No.: (empty)</t>
   </si>
   <si>
-    <t>Serial No. field shows a red error message under the input box (required); not saved, modal stays open</t>
+    <t>"Please fill in: Serial No." error shown under Serial No. field; not saved, modal stays open</t>
   </si>
   <si>
     <t>TA-01_TC-03</t>
@@ -585,7 +585,7 @@
     <t>Spare Part: (empty)</t>
   </si>
   <si>
-    <t>Spare Part field shows a red error message under the input box (required); not saved</t>
+    <t>"Please fill in: Spare Part" error shown under Spare Part field; not saved</t>
   </si>
   <si>
     <t>TA-02</t>
